--- a/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_1_['No. 51_～と〈条件(じょうけん)〉 ']_revised_iteration_3.xlsx
+++ b/docs/revised_shatin/qwen3-next-80b-a3b-instruct/test_grammar_1_['No. 51_～と〈条件(じょうけん)〉 ']_revised_iteration_3.xlsx
@@ -472,15 +472,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1. から
-2. と
-3. たら
-4. ので</t>
+          <t>1. ので 2. から 3. と 4. たら</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr"/>
@@ -494,7 +491,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 この道をまっすぐ行く (   )、駅があります。</t>
+          <t>: もんだい1 この道をまっすぐ行く (   )、駅があります。</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -523,15 +520,12 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>1. から
-2. ので
-3. たら
-4. と</t>
+          <t>1. ので 2. と 3. から 4. たら</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr"/>
@@ -545,7 +539,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 このボタンを押す (   )、ドアが開きます。</t>
+          <t>: もんだい1 このボタンを押す (   )、ドアが開きます。</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -574,15 +568,12 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1. から
-2. ので
-3. たら
-4. と</t>
+          <t>1. ので 2. と 3. から 4. たら</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr"/>
@@ -601,15 +592,12 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>1. と
-2. ので
-3. たら
-4. から</t>
+          <t>1. ので 2. たら 3. から 4. なら</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr"/>
@@ -623,20 +611,17 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 電車が止まる (   )、すぐに降りてください。</t>
+          <t>: もんだい1 店に入る (   )、すぐに店員が来ました。</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>1. と
-2. ので
-3. たら
-4. から</t>
+          <t>1. ので 2. と 3. から 4. たら</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr"/>
@@ -650,20 +635,17 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 ドアを開ける (   )、猫が飛び出してきました。</t>
+          <t>: もんだい1 道を歩いている (   )、友達に会いました。</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1. と
-2. ので
-3. たら
-4. から</t>
+          <t>1. ので 2. と 3. から 4. たら</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr"/>
@@ -677,17 +659,17 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい1 ボタンを押す (   )、電気が消えます。</t>
+          <t>: もんだい1 ボタンを押す (   )、電気が消えます。</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1. ので 2. と 3. から 4. たら</t>
+          <t>1. ので 2. たら 3. から 4. と</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr"/>
@@ -701,7 +683,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 私は 朝 起きる (   )、まず コーヒーを 飲みます。</t>
+          <t>: もんだい2 私は 朝 起きる (   )、まず コーヒーを 飲みます。</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -720,12 +702,12 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Q11</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 このボタンを 押す (   )、ドアが 開きます。</t>
+          <t>: もんだい2 このボタンを 押す (   )、ドアが 開きます。</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -744,12 +726,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Q12</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 雨が 降る (   )、試合は 中止になります。</t>
+          <t>: もんだい2 雨が 降る (   )、試合は 中止になります。</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -768,12 +750,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q13</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 彼は 家に 帰る (   )、すぐに 寝ます。</t>
+          <t>: もんだい2 彼は 家に 帰る (   )、すぐに 寝ます。</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -792,12 +774,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Q14</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 ボタンを 押す (   )、音楽が 流れます。</t>
+          <t>: もんだい2 ボタンを 押す (   )、音楽が 流れます。</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -816,12 +798,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Q15</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 この道を まっすぐ 行く (   )、駅に 着きます。</t>
+          <t>: もんだい2 この道を まっすぐ 行く (   )、駅に 着きます。</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -840,12 +822,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Q16</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 春が 来る (   )、桜が 咲きます。</t>
+          <t>: もんだい2 春が 来る (   )、桜が 咲きます。</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -864,17 +846,17 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Q17</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 信号が 青に なる (   )、渡りましょう。</t>
+          <t>: もんだい2 信号が 青に なる (   )、渡りましょう。</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>1. で 2. に 3. と 4. が</t>
+          <t>1. で 2. に 3. なら 4. が</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -888,12 +870,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Q18</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 電車が 来る (   )、ホームに 並びます。</t>
+          <t>: もんだい2 電車が 来る (   )、ホームに 並びます。</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -912,12 +894,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Q19</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい2 この薬を 飲む (   )、頭痛が 治ります。</t>
+          <t>: もんだい2 この薬を 飲む (   )、頭痛が 治ります。</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -936,12 +918,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q20</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 天気予報によると、明日は雨が(   )そうです。</t>
+          <t>: もんだい3 天気予報によると、明日は雨が(   )そうです。</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -960,12 +942,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Q21</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 このボタンを押すと、テレビが(   )。</t>
+          <t>: もんだい3 このボタンを押すと、テレビが(   )。</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -984,22 +966,22 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Q22</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 先生の話を聞くと、(   )ことが多いです。</t>
+          <t>: もんだい3 先生の話を聞くと、(   )ことが多いです。</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>1. 学ぶ 2. 学び 3. 学んだ 4. 学んで</t>
+          <t>1. 学べる 2. 学び 3. 学んだ 4. 学んで</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr"/>
@@ -1008,12 +990,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Q23</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 この道をまっすぐ行くと、駅が(   )。</t>
+          <t>: もんだい3 この道をまっすぐ行くと、駅が(   )。</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1032,12 +1014,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Q24</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 お金がないと、(   )ことができません。</t>
+          <t>: もんだい3 お金がないと、(   )ことができません。</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1056,12 +1038,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Q25</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 夏になると、(   )が食べたくなります。</t>
+          <t>: もんだい3 夏になると、(   )が食べたくなります。</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1080,12 +1062,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Q26</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 この本を読むと、(   )が広がります。</t>
+          <t>: もんだい3 この本を読むと、(   )が広がります。</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1104,12 +1086,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Q27</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 友達に会うと、いつも(   )。</t>
+          <t>: もんだい3 友達に会うと、いつも(   )。</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1128,17 +1110,17 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Q28</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 家を出ると、すぐに雨が(   )。</t>
+          <t>: もんだい3 家を出ると、すぐに雨が(   )。</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>1. ふる 2. ふって 3. ふり 4. ふった</t>
+          <t>1. ふった 2. ふる 3. ふり 4. ふって</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1152,17 +1134,17 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Q29</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい3 この薬を飲むと、頭痛が(   )。</t>
+          <t>: もんだい3 この薬を飲むと、頭痛が(   )。</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>1. なおる 2. なおり 3. なおって 4. なおらない</t>
+          <t>1. なおる 2. なおらない 3. なおり 4. なおって</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1176,12 +1158,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Q30</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 雨が 降ったら、 ピクニックは (   ).</t>
+          <t>: もんだい4 もし 雨が 降ったら、 ピクニックは (   )。</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1200,12 +1182,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Q31</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 財布を 忘れると、 買い物が (   ).</t>
+          <t>: もんだい4 財布を 忘れると、 買い物が (   )。</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1224,12 +1206,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Q32</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 試験に 合格したら、 新しいパソコンを (   ).</t>
+          <t>: もんだい4 もし 試験に 合格したら、 新しいパソコンを (   )。</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1248,12 +1230,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Q33</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼女に 会うと、 いつも (   ).</t>
+          <t>: もんだい4 彼女に 会うと、 いつも (   )。</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1272,12 +1254,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Q34</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 時間が あったら、 一緒に 映画を (   ).</t>
+          <t>: もんだい4 もし 時間が あったら、 一緒に 映画を (   )。</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1296,22 +1278,22 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Q35</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 宿題を 終わらせると、 友達と (   ).</t>
+          <t>: もんだい4 宿題を 終わらせると、 友達と (   )。</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>1. 遊びたい 2. 遊びに行くことにした 3. 遊ぶかもしれない 4. 遊びたがる</t>
+          <t>1. 遊びたい 2. 遊ぶ 3. 遊びたがる 4. 遊びに行くことにした</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr"/>
@@ -1320,12 +1302,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Q36</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし 電車が 遅れたら、 タクシーで (   ).</t>
+          <t>: もんだい4 もし 電車が 遅れたら、 タクシーで (   )。</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1335,7 +1317,7 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr"/>
@@ -1344,12 +1326,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Q37</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 彼に 会ったら、 すぐに (   ).</t>
+          <t>: もんだい4 彼に 会ったら、 すぐに (   )。</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1368,12 +1350,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Q38</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 もし お金が 足りなかったら、 アルバイトを (   ).</t>
+          <t>: もんだい4 もし お金が 足りなかったら、 アルバイトを (   )。</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1383,7 +1365,7 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr"/>
@@ -1392,22 +1374,22 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Q39</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい4 試合に 勝ったら、 みんなで (   ).</t>
+          <t>: もんだい4 試合に 勝ったら、 みんなで (   )。</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>1. お祝いすることにした 2. お祝いしたがる 3. お祝いしようと思う 4. お祝いするそうだ</t>
+          <t>1. お祝いする 2. お祝いしたがる 3. お祝いしようと思う 4. お祝いするそうだ</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr"/>
@@ -1416,12 +1398,12 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Q40</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 雨が降る (   )、試合は中止になります。</t>
+          <t>: もんだい5 雨が降る (   )、試合は中止になります。</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1440,12 +1422,12 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Q41</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 彼が来る (   )、パーティーを始めます。</t>
+          <t>: もんだい5 彼が来る (   )、パーティーを始めます。</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1464,12 +1446,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Q42</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 お金を持っている (   )、買い物に行けます。</t>
+          <t>: もんだい5 お金を持っている (   )、買い物に行けます。</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1488,12 +1470,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Q43</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 時間がある (   )、映画を見に行きましょう。</t>
+          <t>: もんだい5 時間がある (   )、映画を見に行きましょう。</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1512,12 +1494,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Q44</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 このボタンを押す (   )、ドアが開きます。</t>
+          <t>: もんだい5 このボタンを押す (   )、ドアが開きます。</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1536,12 +1518,12 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Q45</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 朝ごはんを食べる (   )、元気が出ます。</t>
+          <t>: もんだい5 朝ごはんを食べる (   )、元気が出ます。</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1560,12 +1542,12 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Q46</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 電話をかける (   )、彼はすぐ来ます。</t>
+          <t>: もんだい5 電話をかける (   )、彼はすぐ来ます。</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1584,12 +1566,12 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Q47</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 春になる (   )、桜が咲きます。</t>
+          <t>: もんだい5 春になる (   )、桜が咲きます。</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1608,12 +1590,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Q48</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 この薬を飲む (   )、風邪が治ります。</t>
+          <t>: もんだい5 この薬を飲む (   )、風邪が治ります。</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1632,12 +1614,12 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Q49</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい5 音楽を聞く (   )、気分が良くなります。</t>
+          <t>: もんだい5 音楽を聞く (   )、気分が良くなります。</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1656,12 +1638,12 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Q50</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「このボタンをおすと どうなりますか。 」 B:「ドアが (   )。 」</t>
+          <t>: もんだい6 A:「このボタンをおすと どうなりますか。 」 B:「ドアが (   )。 」</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1680,12 +1662,12 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Q51</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「雨がふると かさを(   )。 」 B:「そうですね。 」</t>
+          <t>: もんだい6 A:「雨がふると かさを(   )。 」 B:「そうですね。 」</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1704,12 +1686,12 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Q52</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「この薬を飲むと、どうなりますか。 」 B:「すぐに (   )。 」</t>
+          <t>: もんだい6 A:「この薬を飲むと、どうなりますか。 」 B:「すぐに (   )。 」</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1728,12 +1710,12 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Q53</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「お金を入れると ジュースが(   )。 」 B:「わかりました。 」</t>
+          <t>: もんだい6 A:「お金を入れると ジュースが(   )。 」 B:「わかりました。 」</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -1752,12 +1734,12 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Q54</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「この道をまっすぐ行くと、右に何がありますか。 」 B:「(   )。 」</t>
+          <t>: もんだい6 A:「この道をまっすぐ行くと、右に何がありますか。 」 B:「(   )。 」</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1776,12 +1758,12 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Q55</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「天気がいいと、何をしますか。 」 B:「公園で(   )。 」</t>
+          <t>: もんだい6 A:「天気がいいと、何をしますか。 」 B:「公園で(   )。 」</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1800,12 +1782,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>Q56</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「日本に行くと、日本語が(   )。 」 B:「そうですね。 」</t>
+          <t>: もんだい6 A:「日本に行くと、日本語が(   )。 」 B:「そうですね。 」</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1824,12 +1806,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>Q57</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「このボタンをおすと、どうなるの？ 」 B:「テレビが(   )。 」</t>
+          <t>: もんだい6 A:「このボタンをおすと、どうなるの？ 」 B:「テレビが(   )。 」</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1848,12 +1830,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>Q58</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「夜になると、どうなる？ 」 B:「道が(   )。 」</t>
+          <t>: もんだい6 A:「夜になると、どうなる？ 」 B:「道が(   )。 」</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1872,12 +1854,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Q59</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい6 A:「お金がたくさんあると、どうしますか。 」 B:「旅行に(   )。 」</t>
+          <t>: もんだい6 A:「お金がたくさんあると、どうしますか。 」 B:「旅行に(   )。 」</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1896,12 +1878,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Q60</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 雨が降ると、(   )。</t>
+          <t>: もんだい7 雨が降ると、(   )。</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -1920,12 +1902,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>Q61</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 毎日運動をすると、(   )。</t>
+          <t>: もんだい7 毎日運動をすると、(   )。</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1944,12 +1926,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>Q62</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 このボタンを押すと、(   )。</t>
+          <t>: もんだい7 このボタンを押すと、(   )。</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1968,12 +1950,12 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>Q63</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 夏になると、(   )。</t>
+          <t>: もんだい7 夏になると、(   )。</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -1992,12 +1974,12 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Q64</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 勉強しないと、(   )。</t>
+          <t>: もんだい7 勉強しないと、(   )。</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2016,12 +1998,12 @@
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>Q65</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 冬になると、(   )。</t>
+          <t>: もんだい7 冬になると、(   )。</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2040,12 +2022,12 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Q66</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 時間があるときは、(   )。</t>
+          <t>: もんだい7 時間があるときは、(   )。</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2064,12 +2046,12 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>Q67</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 お金がないと、(   )。</t>
+          <t>: もんだい7 お金がないと、(   )。</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2088,12 +2070,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Q68</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 毎日日本語を勉強すると、(   )。</t>
+          <t>: もんだい7 毎日日本語を勉強すると、(   )。</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2112,12 +2094,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Q69</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい7 練習を続けると、(   )。</t>
+          <t>: もんだい7 練習を続けると、(   )。</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2136,22 +2118,22 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>Q70</t>
+          <t>Q10</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 雨が降る (ふる) と (   )、気温 (きおん) が下がる。</t>
+          <t>: もんだい8 雨が降ると、気温が(   )。</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>1. みたい 2. らしく 3. ように 4. ほどに</t>
+          <t>1. 上がる 2. 下がる 3. 変わらない 4. 消える</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr"/>
@@ -2160,12 +2142,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>Q71</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 春になる (   )、花が咲きます。</t>
+          <t>: もんだい8 春になる (   )、花が咲きます。</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2184,12 +2166,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>Q72</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 このボタンを押す (   )、ドアが開きます。</t>
+          <t>: もんだい8 このボタンを押す (   )、ドアが開きます。</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2208,12 +2190,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Q73</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 夜になる (   )、星が見えます。</t>
+          <t>: もんだい8 夜になる (   )、星が見えます。</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2232,12 +2214,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Q74</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 朝ご飯を食べる (   )、元気になります。</t>
+          <t>: もんだい8 朝ご飯を食べる (   )、元気になります。</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2256,12 +2238,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>Q75</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 音楽を聴く (   )、リラックスできます。</t>
+          <t>: もんだい8 音楽を聴く (   )、リラックスできます。</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2280,12 +2262,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>Q76</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 部屋が静かだ (   )、よく集中できます。</t>
+          <t>: もんだい8 部屋が静かだ (   )、よく集中できます。</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2304,12 +2286,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>Q77</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 この薬を飲む (   )、すぐに治ります。</t>
+          <t>: もんだい8 この薬を飲む (   )、すぐに治ります。</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2328,12 +2310,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>Q78</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 信号が青になる (   )、渡ってください。</t>
+          <t>: もんだい8 信号が青になる (   )、渡ってください。</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2352,12 +2334,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>Q79</t>
+          <t>Q9</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>: もんだい1 : もんだい8 時間がある (   )、一緒に行きませんか。</t>
+          <t>: もんだい8 時間がある (   )、一緒に行きませんか。</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
